--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_pharmaceutical.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0475</v>
+        <v>0.255</v>
       </c>
       <c r="G2">
-        <v>-0.9153976311336717</v>
+        <v>-2.812015503875969</v>
       </c>
       <c r="H2">
-        <v>-4.94077834179357</v>
+        <v>-4.490310077519379</v>
       </c>
       <c r="I2">
-        <v>-4.790293922048515</v>
+        <v>-2.023461486061692</v>
       </c>
       <c r="J2">
-        <v>-4.790293922048515</v>
+        <v>-2.023461486061692</v>
       </c>
       <c r="K2">
-        <v>-225.8</v>
+        <v>850.5</v>
       </c>
       <c r="L2">
-        <v>-3.820642978003384</v>
+        <v>16.48255813953488</v>
       </c>
       <c r="M2">
-        <v>9.42</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N2">
-        <v>0.01156679764243615</v>
+        <v>0.1284294234592445</v>
       </c>
       <c r="O2">
-        <v>-0.04171833480956599</v>
+        <v>0.1139329805996473</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +624,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>9.42</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>121.4</v>
+        <v>418.5</v>
       </c>
       <c r="V2">
-        <v>0.1490667976424362</v>
+        <v>0.5546719681908548</v>
       </c>
       <c r="W2">
-        <v>0.8634799235181645</v>
+        <v>-2.628244746600741</v>
       </c>
       <c r="X2">
-        <v>0.10235688080441</v>
+        <v>0.1140291595419907</v>
       </c>
       <c r="Y2">
-        <v>0.7611230427137545</v>
+        <v>-2.742273906142732</v>
       </c>
       <c r="Z2">
-        <v>0.1728414574852431</v>
+        <v>0.219198506824281</v>
       </c>
       <c r="AA2">
-        <v>-0.8279613832695669</v>
+        <v>-0.4435397363611634</v>
       </c>
       <c r="AB2">
-        <v>0.07031235724939573</v>
+        <v>0.1099577646242468</v>
       </c>
       <c r="AC2">
-        <v>-0.8982737405189627</v>
+        <v>-0.5534975009854102</v>
       </c>
       <c r="AD2">
-        <v>615.9</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>85.5318539653361</v>
+        <v>64.50306340391641</v>
       </c>
       <c r="AF2">
-        <v>701.4318539653361</v>
+        <v>64.50306340391641</v>
       </c>
       <c r="AG2">
-        <v>580.0318539653362</v>
+        <v>-353.9969365960836</v>
       </c>
       <c r="AH2">
-        <v>0.4627372436661939</v>
+        <v>0.07875802458641691</v>
       </c>
       <c r="AI2">
-        <v>1.856465638362213</v>
+        <v>0.118331867374079</v>
       </c>
       <c r="AJ2">
-        <v>0.4159628542018053</v>
+        <v>-0.8838807213793259</v>
       </c>
       <c r="AK2">
-        <v>2.261933706737321</v>
+        <v>-2.796116674259975</v>
       </c>
       <c r="AL2">
-        <v>46.9</v>
+        <v>46.3</v>
       </c>
       <c r="AM2">
-        <v>45.33</v>
+        <v>42.95</v>
       </c>
       <c r="AN2">
-        <v>-2.367935409457901</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-5.891257995735608</v>
+        <v>-2.1792656587473</v>
       </c>
       <c r="AP2">
-        <v>-2.230034040620285</v>
+        <v>4.049844830066166</v>
       </c>
       <c r="AQ2">
-        <v>-6.095301125082727</v>
+        <v>-2.349243306169965</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0475</v>
+        <v>0.255</v>
       </c>
       <c r="G3">
-        <v>-0.9153976311336717</v>
+        <v>-2.812015503875969</v>
       </c>
       <c r="H3">
-        <v>-4.94077834179357</v>
+        <v>-4.490310077519379</v>
       </c>
       <c r="I3">
-        <v>-4.790293922048515</v>
+        <v>-2.023461486061692</v>
       </c>
       <c r="J3">
-        <v>-4.790293922048515</v>
+        <v>-2.023461486061692</v>
       </c>
       <c r="K3">
-        <v>-225.8</v>
+        <v>850.5</v>
       </c>
       <c r="L3">
-        <v>-3.820642978003384</v>
+        <v>16.48255813953488</v>
       </c>
       <c r="M3">
-        <v>9.42</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N3">
-        <v>0.01156679764243615</v>
+        <v>0.1284294234592445</v>
       </c>
       <c r="O3">
-        <v>-0.04171833480956599</v>
+        <v>0.1139329805996473</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,82 +755,82 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>9.42</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>121.4</v>
+        <v>418.5</v>
       </c>
       <c r="V3">
-        <v>0.1490667976424362</v>
+        <v>0.5546719681908548</v>
       </c>
       <c r="W3">
-        <v>0.8634799235181645</v>
+        <v>-2.628244746600741</v>
       </c>
       <c r="X3">
-        <v>0.10235688080441</v>
+        <v>0.1140291595419907</v>
       </c>
       <c r="Y3">
-        <v>0.7611230427137545</v>
+        <v>-2.742273906142732</v>
       </c>
       <c r="Z3">
-        <v>0.1728414574852431</v>
+        <v>0.219198506824281</v>
       </c>
       <c r="AA3">
-        <v>-0.8279613832695669</v>
+        <v>-0.4435397363611634</v>
       </c>
       <c r="AB3">
-        <v>0.07031235724939573</v>
+        <v>0.1099577646242468</v>
       </c>
       <c r="AC3">
-        <v>-0.8982737405189627</v>
+        <v>-0.5534975009854102</v>
       </c>
       <c r="AD3">
-        <v>615.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>85.5318539653361</v>
+        <v>64.50306340391641</v>
       </c>
       <c r="AF3">
-        <v>701.4318539653361</v>
+        <v>64.50306340391641</v>
       </c>
       <c r="AG3">
-        <v>580.0318539653362</v>
+        <v>-353.9969365960836</v>
       </c>
       <c r="AH3">
-        <v>0.4627372436661939</v>
+        <v>0.07875802458641691</v>
       </c>
       <c r="AI3">
-        <v>1.856465638362213</v>
+        <v>0.118331867374079</v>
       </c>
       <c r="AJ3">
-        <v>0.4159628542018053</v>
+        <v>-0.8838807213793259</v>
       </c>
       <c r="AK3">
-        <v>2.261933706737321</v>
+        <v>-2.796116674259975</v>
       </c>
       <c r="AL3">
-        <v>46.9</v>
+        <v>46.3</v>
       </c>
       <c r="AM3">
-        <v>45.33</v>
+        <v>42.95</v>
       </c>
       <c r="AN3">
-        <v>-2.367935409457901</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-5.891257995735608</v>
+        <v>-2.1792656587473</v>
       </c>
       <c r="AP3">
-        <v>-2.230034040620285</v>
+        <v>4.049844830066166</v>
       </c>
       <c r="AQ3">
-        <v>-6.095301125082727</v>
+        <v>-2.349243306169965</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_drugs_pharmaceutical.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.255</v>
+        <v>0.0209</v>
       </c>
       <c r="G2">
-        <v>-2.812015503875969</v>
+        <v>-0.3944954128440366</v>
       </c>
       <c r="H2">
-        <v>-4.490310077519379</v>
+        <v>-1.396330275229358</v>
       </c>
       <c r="I2">
-        <v>-2.023461486061692</v>
+        <v>-1.243010567791176</v>
       </c>
       <c r="J2">
-        <v>-2.023461486061692</v>
+        <v>-1.243010567791176</v>
       </c>
       <c r="K2">
-        <v>850.5</v>
+        <v>-57</v>
       </c>
       <c r="L2">
-        <v>16.48255813953488</v>
+        <v>-1.045871559633027</v>
       </c>
       <c r="M2">
-        <v>96.90000000000001</v>
+        <v>204.6</v>
       </c>
       <c r="N2">
-        <v>0.1284294234592445</v>
+        <v>0.3655529748079328</v>
       </c>
       <c r="O2">
-        <v>0.1139329805996473</v>
+        <v>-3.589473684210526</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +624,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>96.90000000000001</v>
+        <v>204.6</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>418.5</v>
+        <v>71.7</v>
       </c>
       <c r="V2">
-        <v>0.5546719681908548</v>
+        <v>0.1281043416115776</v>
       </c>
       <c r="W2">
-        <v>-2.628244746600741</v>
+        <v>-0.118601747815231</v>
       </c>
       <c r="X2">
-        <v>0.1140291595419907</v>
+        <v>0.09292758373091241</v>
       </c>
       <c r="Y2">
-        <v>-2.742273906142732</v>
+        <v>-0.2115293315461434</v>
       </c>
       <c r="Z2">
-        <v>0.219198506824281</v>
+        <v>0.4255472664158246</v>
       </c>
       <c r="AA2">
-        <v>-0.4435397363611634</v>
+        <v>-0.5289597492495172</v>
       </c>
       <c r="AB2">
-        <v>0.1099577646242468</v>
+        <v>0.08856720593618533</v>
       </c>
       <c r="AC2">
-        <v>-0.5534975009854102</v>
+        <v>-0.6175269551857026</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>64.50306340391641</v>
+        <v>65.9703797230956</v>
       </c>
       <c r="AF2">
-        <v>64.50306340391641</v>
+        <v>65.9703797230956</v>
       </c>
       <c r="AG2">
-        <v>-353.9969365960836</v>
+        <v>-5.729620276904399</v>
       </c>
       <c r="AH2">
-        <v>0.07875802458641691</v>
+        <v>0.1054395123392165</v>
       </c>
       <c r="AI2">
-        <v>0.118331867374079</v>
+        <v>0.2113958389182339</v>
       </c>
       <c r="AJ2">
-        <v>-0.8838807213793259</v>
+        <v>-0.01034282785980069</v>
       </c>
       <c r="AK2">
-        <v>-2.796116674259975</v>
+        <v>-0.02383663196565595</v>
       </c>
       <c r="AL2">
-        <v>46.3</v>
+        <v>2.28</v>
       </c>
       <c r="AM2">
-        <v>42.95</v>
+        <v>-5.4</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-2.1792656587473</v>
+        <v>-28.28947368421053</v>
       </c>
       <c r="AP2">
-        <v>4.049844830066166</v>
+        <v>0.1060059255671489</v>
       </c>
       <c r="AQ2">
-        <v>-2.349243306169965</v>
+        <v>11.94444444444444</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.255</v>
+        <v>0.0209</v>
       </c>
       <c r="G3">
-        <v>-2.812015503875969</v>
+        <v>-0.3944954128440366</v>
       </c>
       <c r="H3">
-        <v>-4.490310077519379</v>
+        <v>-1.396330275229358</v>
       </c>
       <c r="I3">
-        <v>-2.023461486061692</v>
+        <v>-1.243010567791176</v>
       </c>
       <c r="J3">
-        <v>-2.023461486061692</v>
+        <v>-1.243010567791176</v>
       </c>
       <c r="K3">
-        <v>850.5</v>
+        <v>-57</v>
       </c>
       <c r="L3">
-        <v>16.48255813953488</v>
+        <v>-1.045871559633027</v>
       </c>
       <c r="M3">
-        <v>96.90000000000001</v>
+        <v>204.6</v>
       </c>
       <c r="N3">
-        <v>0.1284294234592445</v>
+        <v>0.3655529748079328</v>
       </c>
       <c r="O3">
-        <v>0.1139329805996473</v>
+        <v>-3.589473684210526</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,82 +755,82 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>96.90000000000001</v>
+        <v>204.6</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>418.5</v>
+        <v>71.7</v>
       </c>
       <c r="V3">
-        <v>0.5546719681908548</v>
+        <v>0.1281043416115776</v>
       </c>
       <c r="W3">
-        <v>-2.628244746600741</v>
+        <v>-0.118601747815231</v>
       </c>
       <c r="X3">
-        <v>0.1140291595419907</v>
+        <v>0.09292758373091241</v>
       </c>
       <c r="Y3">
-        <v>-2.742273906142732</v>
+        <v>-0.2115293315461434</v>
       </c>
       <c r="Z3">
-        <v>0.219198506824281</v>
+        <v>0.4255472664158246</v>
       </c>
       <c r="AA3">
-        <v>-0.4435397363611634</v>
+        <v>-0.5289597492495172</v>
       </c>
       <c r="AB3">
-        <v>0.1099577646242468</v>
+        <v>0.08856720593618533</v>
       </c>
       <c r="AC3">
-        <v>-0.5534975009854102</v>
+        <v>-0.6175269551857026</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>64.50306340391641</v>
+        <v>65.9703797230956</v>
       </c>
       <c r="AF3">
-        <v>64.50306340391641</v>
+        <v>65.9703797230956</v>
       </c>
       <c r="AG3">
-        <v>-353.9969365960836</v>
+        <v>-5.729620276904399</v>
       </c>
       <c r="AH3">
-        <v>0.07875802458641691</v>
+        <v>0.1054395123392165</v>
       </c>
       <c r="AI3">
-        <v>0.118331867374079</v>
+        <v>0.2113958389182339</v>
       </c>
       <c r="AJ3">
-        <v>-0.8838807213793259</v>
+        <v>-0.01034282785980069</v>
       </c>
       <c r="AK3">
-        <v>-2.796116674259975</v>
+        <v>-0.02383663196565595</v>
       </c>
       <c r="AL3">
-        <v>46.3</v>
+        <v>2.28</v>
       </c>
       <c r="AM3">
-        <v>42.95</v>
+        <v>-5.4</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-2.1792656587473</v>
+        <v>-28.28947368421053</v>
       </c>
       <c r="AP3">
-        <v>4.049844830066166</v>
+        <v>0.1060059255671489</v>
       </c>
       <c r="AQ3">
-        <v>-2.349243306169965</v>
+        <v>11.94444444444444</v>
       </c>
     </row>
   </sheetData>
